--- a/data/trans_dic/P36$cafe-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36$cafe-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,...</t>
+          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,39; 91,97</t>
+          <t>83,51; 91,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,39; 93,39</t>
+          <t>86,35; 93,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,48; 88,77</t>
+          <t>79,56; 88,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78,45; 88,0</t>
+          <t>78,45; 88,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,54; 92,4</t>
+          <t>84,01; 92,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,29; 93,69</t>
+          <t>87,03; 93,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,45; 88,67</t>
+          <t>82,37; 88,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>86,69; 91,91</t>
+          <t>87,04; 92,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84,26; 90,16</t>
+          <t>84,74; 90,44</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,49; 89,75</t>
+          <t>83,55; 89,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,9; 90,56</t>
+          <t>84,69; 90,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,62; 92,04</t>
+          <t>86,68; 92,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85,27; 91,11</t>
+          <t>85,73; 91,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,06; 94,08</t>
+          <t>89,14; 94,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,32; 93,98</t>
+          <t>89,25; 94,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,68; 89,66</t>
+          <t>85,42; 89,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88,02; 91,64</t>
+          <t>87,85; 91,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,68; 92,39</t>
+          <t>88,87; 92,49</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93,47; 98,17</t>
+          <t>93,51; 98,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,55; 96,85</t>
+          <t>91,57; 96,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,21; 96,06</t>
+          <t>90,58; 96,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93,95; 98,18</t>
+          <t>93,94; 98,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,39; 94,75</t>
+          <t>88,21; 94,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92,19; 96,92</t>
+          <t>92,2; 96,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,49; 97,74</t>
+          <t>94,73; 97,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91,1; 95,11</t>
+          <t>91,17; 95,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92,0; 95,87</t>
+          <t>92,14; 95,76</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,02; 92,59</t>
+          <t>85,88; 92,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,72; 94,01</t>
+          <t>87,36; 93,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,91; 93,23</t>
+          <t>86,65; 93,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89,92; 95,16</t>
+          <t>89,78; 95,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,96; 98,48</t>
+          <t>95,16; 98,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,55; 96,39</t>
+          <t>90,85; 96,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,82; 93,16</t>
+          <t>88,92; 93,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92,07; 95,77</t>
+          <t>92,24; 95,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89,67; 93,99</t>
+          <t>90,11; 94,32</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,99; 96,37</t>
+          <t>90,16; 96,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,55; 96,45</t>
+          <t>88,68; 96,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,94; 93,6</t>
+          <t>86,24; 94,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93,98; 98,94</t>
+          <t>94,24; 99,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,47; 96,99</t>
+          <t>90,99; 97,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,42; 94,87</t>
+          <t>87,58; 94,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,33; 97,21</t>
+          <t>93,07; 97,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>91,24; 96,21</t>
+          <t>91,38; 95,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>88,14; 93,66</t>
+          <t>88,15; 93,45</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92,02; 97,26</t>
+          <t>92,34; 97,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,68; 93,71</t>
+          <t>86,24; 93,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81,0; 89,69</t>
+          <t>80,83; 89,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90,14; 96,05</t>
+          <t>89,46; 95,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91,93; 97,36</t>
+          <t>92,01; 97,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88,42; 94,61</t>
+          <t>87,72; 94,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,09; 96,03</t>
+          <t>92,1; 95,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90,28; 95,12</t>
+          <t>90,49; 95,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>85,71; 91,5</t>
+          <t>85,88; 91,25</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>91,46; 95,59</t>
+          <t>91,12; 95,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,71; 92,82</t>
+          <t>88,15; 92,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90,74; 94,83</t>
+          <t>90,56; 94,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91,41; 95,38</t>
+          <t>91,45; 95,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,8; 94,66</t>
+          <t>90,5; 94,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,09; 97,04</t>
+          <t>93,86; 97,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,14; 94,86</t>
+          <t>92,1; 94,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>89,98; 93,14</t>
+          <t>90,11; 93,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>93,04; 95,58</t>
+          <t>93,07; 95,54</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>88,54; 92,76</t>
+          <t>88,45; 92,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>91,82; 95,38</t>
+          <t>91,77; 95,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90,85; 94,72</t>
+          <t>90,7; 94,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87,14; 91,65</t>
+          <t>87,13; 91,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>93,38; 96,52</t>
+          <t>93,41; 96,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,28; 95,61</t>
+          <t>92,33; 95,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,53; 91,68</t>
+          <t>88,71; 91,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>93,28; 95,68</t>
+          <t>93,24; 95,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>92,35; 94,76</t>
+          <t>92,3; 94,67</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>90,48; 92,43</t>
+          <t>90,33; 92,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>90,44; 92,4</t>
+          <t>90,49; 92,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89,7; 91,82</t>
+          <t>89,74; 91,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>90,66; 92,53</t>
+          <t>90,53; 92,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>92,69; 94,4</t>
+          <t>92,72; 94,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>92,74; 94,38</t>
+          <t>92,74; 94,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>90,89; 92,16</t>
+          <t>90,79; 92,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>91,92; 93,2</t>
+          <t>91,89; 93,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>91,51; 92,85</t>
+          <t>91,62; 92,88</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,...</t>
+          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>226196; 249464</t>
+          <t>226526; 248253</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>254622; 275252</t>
+          <t>254502; 275736</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>233486; 260763</t>
+          <t>233703; 260899</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>203791; 228580</t>
+          <t>203782; 228999</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>242047; 264554</t>
+          <t>240517; 263804</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>249132; 270477</t>
+          <t>251270; 269877</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>437840; 470823</t>
+          <t>437405; 470279</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>503686; 534066</t>
+          <t>505723; 535998</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>490755; 525153</t>
+          <t>493608; 526754</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>410789; 441585</t>
+          <t>411096; 441297</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>428302; 456872</t>
+          <t>427272; 456482</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>433451; 460562</t>
+          <t>433747; 462242</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>429721; 459163</t>
+          <t>432035; 459673</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>464647; 490834</t>
+          <t>465061; 491114</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>467195; 491602</t>
+          <t>466835; 492300</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>853349; 892972</t>
+          <t>850798; 893972</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>903238; 940426</t>
+          <t>901558; 942804</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>907586; 945554</t>
+          <t>909583; 946582</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>298027; 312995</t>
+          <t>298153; 312837</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>295822; 312955</t>
+          <t>295898; 313271</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>287368; 306002</t>
+          <t>288566; 305808</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315106; 329297</t>
+          <t>315074; 329227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>301424; 323118</t>
+          <t>300823; 323120</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>310033; 325943</t>
+          <t>310067; 325948</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>618188; 639498</t>
+          <t>619806; 640380</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>605034; 631670</t>
+          <t>605501; 632291</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>602468; 627818</t>
+          <t>603402; 627110</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>307680; 331190</t>
+          <t>307175; 332131</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>327092; 350567</t>
+          <t>325776; 350137</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>321538; 344907</t>
+          <t>320567; 345585</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>333997; 353462</t>
+          <t>333489; 352975</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>369337; 383036</t>
+          <t>370127; 383052</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>354567; 373286</t>
+          <t>351834; 372753</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>647607; 679303</t>
+          <t>648378; 679503</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>701433; 729629</t>
+          <t>702708; 730147</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>679040; 711721</t>
+          <t>682381; 714223</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>182158; 195054</t>
+          <t>182491; 195474</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>188268; 205061</t>
+          <t>188546; 205639</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181525; 197704</t>
+          <t>182163; 199064</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>194223; 204479</t>
+          <t>194767; 204610</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>198661; 212974</t>
+          <t>199801; 213482</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>191090; 207375</t>
+          <t>191446; 207210</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>381810; 397673</t>
+          <t>380735; 397789</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>394366; 415840</t>
+          <t>394940; 414556</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>378850; 402574</t>
+          <t>378896; 401648</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>249195; 263396</t>
+          <t>250055; 263780</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>234734; 256749</t>
+          <t>236274; 257271</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>213121; 235998</t>
+          <t>212681; 236021</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>250707; 267163</t>
+          <t>248835; 266156</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>256490; 271624</t>
+          <t>256702; 271546</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>240428; 257268</t>
+          <t>238527; 257941</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>505545; 527163</t>
+          <t>505577; 526907</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>499250; 525975</t>
+          <t>500398; 525370</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>458581; 489542</t>
+          <t>459476; 488207</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>560632; 585985</t>
+          <t>558550; 584933</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>581323; 615205</t>
+          <t>584272; 615145</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>594161; 620951</t>
+          <t>592966; 621221</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>581629; 606847</t>
+          <t>581870; 607135</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>629992; 656778</t>
+          <t>627912; 656130</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>648519; 668810</t>
+          <t>646934; 669594</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1151128; 1185000</t>
+          <t>1150553; 1186306</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1220697; 1263605</t>
+          <t>1222443; 1265375</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1250471; 1284615</t>
+          <t>1250869; 1284026</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>658537; 689967</t>
+          <t>657905; 690044</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>712759; 740364</t>
+          <t>712352; 739777</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>707341; 737438</t>
+          <t>706162; 737229</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>682789; 718097</t>
+          <t>682667; 717531</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>767335; 793156</t>
+          <t>767582; 793144</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>762385; 789917</t>
+          <t>762837; 790626</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1352193; 1400228</t>
+          <t>1354905; 1402173</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1490614; 1528882</t>
+          <t>1489985; 1528000</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1481907; 1520609</t>
+          <t>1481178; 1519215</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2958647; 3022335</t>
+          <t>2953472; 3020686</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3093794; 3160962</t>
+          <t>3095519; 3160006</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3041234; 3112948</t>
+          <t>3042692; 3113510</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3060053; 3122923</t>
+          <t>3055452; 3122071</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3292647; 3353261</t>
+          <t>3293620; 3348714</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3284294; 3342354</t>
+          <t>3284043; 3342862</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6039320; 6124212</t>
+          <t>6033195; 6125749</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>6409528; 6498596</t>
+          <t>6407334; 6499895</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6343469; 6435749</t>
+          <t>6350672; 6437806</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$cafe-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36$cafe-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,51; 91,52</t>
+          <t>82,67; 91,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,35; 93,55</t>
+          <t>86,54; 93,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,56; 88,81</t>
+          <t>80,17; 89,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78,45; 88,16</t>
+          <t>78,34; 87,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,01; 92,14</t>
+          <t>84,35; 92,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,03; 93,48</t>
+          <t>86,95; 93,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,37; 88,56</t>
+          <t>82,5; 88,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,04; 92,25</t>
+          <t>86,66; 91,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84,74; 90,44</t>
+          <t>84,76; 90,26</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,55; 89,69</t>
+          <t>83,1; 89,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,69; 90,48</t>
+          <t>84,65; 90,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,68; 92,38</t>
+          <t>86,59; 91,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85,73; 91,21</t>
+          <t>85,59; 90,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,14; 94,13</t>
+          <t>89,54; 94,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,25; 94,11</t>
+          <t>89,16; 93,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,42; 89,76</t>
+          <t>85,33; 89,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,85; 91,87</t>
+          <t>87,83; 91,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,87; 92,49</t>
+          <t>88,73; 92,47</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93,51; 98,12</t>
+          <t>93,61; 98,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,57; 96,95</t>
+          <t>91,31; 96,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,58; 96,0</t>
+          <t>90,16; 95,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93,94; 98,16</t>
+          <t>94,12; 98,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,21; 94,75</t>
+          <t>88,4; 94,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92,2; 96,92</t>
+          <t>91,96; 96,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,73; 97,88</t>
+          <t>94,58; 97,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91,17; 95,2</t>
+          <t>90,81; 95,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92,14; 95,76</t>
+          <t>92,12; 95,81</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,88; 92,85</t>
+          <t>85,57; 92,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,36; 93,9</t>
+          <t>87,54; 94,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,65; 93,41</t>
+          <t>86,85; 93,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89,78; 95,02</t>
+          <t>89,75; 94,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,16; 98,48</t>
+          <t>95,22; 98,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,85; 96,25</t>
+          <t>91,22; 96,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,92; 93,19</t>
+          <t>88,91; 93,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92,24; 95,84</t>
+          <t>92,19; 95,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90,11; 94,32</t>
+          <t>90,07; 94,37</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>90,16; 96,57</t>
+          <t>89,98; 96,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,68; 96,72</t>
+          <t>88,65; 96,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,24; 94,24</t>
+          <t>85,61; 93,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94,24; 99,0</t>
+          <t>93,98; 98,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,99; 97,22</t>
+          <t>91,02; 96,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,58; 94,8</t>
+          <t>87,67; 94,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,07; 97,24</t>
+          <t>93,03; 97,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>91,38; 95,92</t>
+          <t>91,16; 96,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>88,15; 93,45</t>
+          <t>87,94; 93,23</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92,34; 97,4</t>
+          <t>92,42; 97,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>86,24; 93,9</t>
+          <t>85,98; 93,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80,83; 89,7</t>
+          <t>81,24; 89,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>89,46; 95,69</t>
+          <t>90,17; 96,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92,01; 97,33</t>
+          <t>92,32; 97,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,72; 94,86</t>
+          <t>87,9; 94,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,1; 95,98</t>
+          <t>92,07; 96,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90,49; 95,01</t>
+          <t>90,3; 94,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>85,88; 91,25</t>
+          <t>85,4; 91,2</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>91,12; 95,42</t>
+          <t>91,43; 95,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>88,15; 92,81</t>
+          <t>88,05; 92,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90,56; 94,88</t>
+          <t>90,48; 94,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91,45; 95,42</t>
+          <t>91,53; 95,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,5; 94,56</t>
+          <t>90,37; 94,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,86; 97,15</t>
+          <t>93,98; 97,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,1; 94,96</t>
+          <t>92,07; 95,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>90,11; 93,27</t>
+          <t>89,94; 93,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>93,07; 95,54</t>
+          <t>92,94; 95,54</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>88,45; 92,77</t>
+          <t>88,65; 92,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>91,77; 95,3</t>
+          <t>91,76; 95,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90,7; 94,69</t>
+          <t>90,97; 94,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87,13; 91,58</t>
+          <t>87,66; 91,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>93,41; 96,52</t>
+          <t>93,3; 96,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,33; 95,7</t>
+          <t>92,37; 95,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,71; 91,81</t>
+          <t>88,69; 91,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>93,24; 95,62</t>
+          <t>93,19; 95,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>92,3; 94,67</t>
+          <t>92,02; 94,7</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>90,33; 92,38</t>
+          <t>90,49; 92,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>90,49; 92,37</t>
+          <t>90,41; 92,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89,74; 91,83</t>
+          <t>89,73; 91,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>90,53; 92,5</t>
+          <t>90,57; 92,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>92,72; 94,27</t>
+          <t>92,69; 94,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>92,74; 94,4</t>
+          <t>92,65; 94,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>90,79; 92,19</t>
+          <t>90,89; 92,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>91,89; 93,21</t>
+          <t>91,89; 93,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>91,62; 92,88</t>
+          <t>91,64; 92,88</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>226526; 248253</t>
+          <t>224230; 247185</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>254502; 275736</t>
+          <t>255078; 275395</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>233703; 260899</t>
+          <t>235500; 261564</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>203782; 228999</t>
+          <t>203489; 227671</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>240517; 263804</t>
+          <t>241494; 263622</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>251270; 269877</t>
+          <t>251038; 270890</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>437405; 470279</t>
+          <t>438079; 471535</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>505723; 535998</t>
+          <t>503519; 533842</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>493608; 526754</t>
+          <t>493718; 525752</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>411096; 441297</t>
+          <t>408904; 439973</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>427272; 456482</t>
+          <t>427036; 457260</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>433747; 462242</t>
+          <t>433301; 460127</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>432035; 459673</t>
+          <t>431307; 458402</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>465061; 491114</t>
+          <t>467150; 490835</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>466835; 492300</t>
+          <t>466389; 491448</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>850798; 893972</t>
+          <t>849888; 891217</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>901558; 942804</t>
+          <t>901353; 941076</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>909583; 946582</t>
+          <t>908079; 946425</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>298153; 312837</t>
+          <t>298471; 313191</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>295898; 313271</t>
+          <t>295035; 312928</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>288566; 305808</t>
+          <t>287208; 305399</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315074; 329227</t>
+          <t>315689; 329326</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>300823; 323120</t>
+          <t>301470; 322602</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>310067; 325948</t>
+          <t>309281; 325821</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>619806; 640380</t>
+          <t>618779; 639559</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>605501; 632291</t>
+          <t>603136; 631263</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>603402; 627110</t>
+          <t>603252; 627430</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>307175; 332131</t>
+          <t>306072; 331474</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>325776; 350137</t>
+          <t>326446; 351337</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>320567; 345585</t>
+          <t>321298; 345482</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>333489; 352975</t>
+          <t>333385; 352512</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>370127; 383052</t>
+          <t>370368; 383088</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>351834; 372753</t>
+          <t>353298; 373557</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>648378; 679503</t>
+          <t>648316; 678104</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>702708; 730147</t>
+          <t>702354; 729087</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>682381; 714223</t>
+          <t>682069; 714583</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>182491; 195474</t>
+          <t>182120; 195539</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>188546; 205639</t>
+          <t>188494; 205380</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182163; 199064</t>
+          <t>180829; 197891</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>194767; 204610</t>
+          <t>194219; 204047</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>199801; 213482</t>
+          <t>199861; 212700</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>191446; 207210</t>
+          <t>191645; 207480</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>380735; 397789</t>
+          <t>380579; 397100</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>394940; 414556</t>
+          <t>394007; 414919</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>378896; 401648</t>
+          <t>377969; 400710</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>250055; 263780</t>
+          <t>250278; 264095</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>236274; 257271</t>
+          <t>235570; 257496</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>212681; 236021</t>
+          <t>213764; 236381</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>248835; 266156</t>
+          <t>250807; 267337</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>256702; 271546</t>
+          <t>257566; 271456</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>238527; 257941</t>
+          <t>239021; 256966</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>505577; 526907</t>
+          <t>505441; 527188</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>500398; 525370</t>
+          <t>499346; 524668</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>459476; 488207</t>
+          <t>456944; 487974</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>558550; 584933</t>
+          <t>560452; 585665</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>584272; 615145</t>
+          <t>583581; 615294</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>592966; 621221</t>
+          <t>592410; 621801</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>581870; 607135</t>
+          <t>582405; 606534</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>627912; 656130</t>
+          <t>627043; 655769</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>646934; 669594</t>
+          <t>647733; 669720</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1150553; 1186306</t>
+          <t>1150230; 1186981</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1222443; 1265375</t>
+          <t>1220217; 1265616</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1250869; 1284026</t>
+          <t>1249077; 1284106</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>657905; 690044</t>
+          <t>659371; 690582</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>712352; 739777</t>
+          <t>712306; 740134</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>706162; 737229</t>
+          <t>708270; 737726</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>682667; 717531</t>
+          <t>686862; 719534</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>767582; 793144</t>
+          <t>766641; 792815</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>762837; 790626</t>
+          <t>763164; 790084</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1354905; 1402173</t>
+          <t>1354572; 1399844</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1489985; 1528000</t>
+          <t>1489158; 1526875</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1481178; 1519215</t>
+          <t>1476660; 1519730</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2953472; 3020686</t>
+          <t>2958997; 3023394</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3095519; 3160006</t>
+          <t>3092777; 3162417</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3042692; 3113510</t>
+          <t>3042248; 3110167</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3055452; 3122071</t>
+          <t>3056925; 3121659</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3293620; 3348714</t>
+          <t>3292393; 3353797</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3284043; 3342862</t>
+          <t>3280832; 3341743</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6033195; 6125749</t>
+          <t>6039299; 6126045</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>6407334; 6499895</t>
+          <t>6407585; 6497022</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6350672; 6437806</t>
+          <t>6352029; 6437817</t>
         </is>
       </c>
     </row>
